--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ESG.xlsx
@@ -422,23 +422,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>36.7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>36.7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ESG_J._BERTINO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Bertino</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -453,24 +720,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>J. Bailey | P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-25.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>J. Bailey | P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-25.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F. Ferreira | P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-30.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F. Ferreira | J. Bailey | P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-34.8</v>
       </c>
     </row>
   </sheetData>
@@ -484,11 +896,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,66 +958,100 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lineups</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>base_lineup</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio (14.9 min)</t>
+          <t>J. Bailey</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lineups</t>
+          <t>scoring</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>best_lineup</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio (10.7 net)</t>
+          <t>J. Bailey</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>lineups</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal (15.3 min)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio (10.7 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
@@ -666,16 +1112,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -685,16 +1131,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.8</v>
+        <v>78.2</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>-28.6</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="4">
@@ -704,16 +1150,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>109.5</v>
+        <v>108.1</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5">
@@ -723,16 +1169,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-27.7</v>
+        <v>-29.8</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>-27.7</v>
+        <v>-29.4</v>
       </c>
     </row>
     <row r="6">
@@ -742,16 +1188,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.2</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="7">
@@ -783,10 +1229,10 @@
         <v>0.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1</v>
@@ -799,16 +1245,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="10">
@@ -824,10 +1270,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="11">
@@ -843,10 +1289,10 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1025,7 +1471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: J. Bailey are the first perimeter names you cannot lose in help situations.</t>
+          <t>Know the first reference: J. Bailey is a primary scorer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1062,12 +1508,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Priority closeouts start with J. Bailey; do not lose them in help-and-recover situations.</t>
+          <t>The main offensive references are J. Bailey and P. Carvalhal; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1079,19 +1525,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from J. Bailey and M. Pombo; contest, but do not over-help into secondary advantages.</t>
+          <t>Priority closeouts start with P. Carvalhal and J. Bailey; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+          <t>Some perimeter volume comes from J. Bailey and M. Pombo; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1103,31 +1549,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially J. Bailey, Y. Antonio, and P. Carvalhal; force them away from preferred areas.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Scoring Areas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+          <t>Several players have clear comfort zones, especially J. Bailey, P. Carvalhal, and Y. Antonio; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: J. Bailey | P. Carvalhal and J. Bailey | P. Carvalhal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Do not lose J. Bailey in help-and-recover situations.</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose P. Carvalhal and J. Bailey in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1142,23 +1612,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>ESG_J._BAILEY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ESG_J._BERTINO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Bertino</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1272,32 +1921,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1313,7 +1962,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1327,23 +1976,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1364,32 +2013,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1410,16 +2059,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_M._POMBO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>M. Pombo</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1428,18 +2077,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1451,74 +2100,94 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>25</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>37.9%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>17</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>25.8%</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1536,23 +2205,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -1572,23 +2241,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -1608,42 +2277,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ESG_J._BAILEY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>J. Bailey</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1652,42 +2313,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ESG_Y._ANTONIO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Y. Antonio</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -1696,23 +2349,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -1724,12 +2377,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1744,19 +2397,195 @@
         </is>
       </c>
       <c r="K13" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ESG_P._CARVALHAL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ESG_D._CARR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>6</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>46.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>35.7%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ESG.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,16 +515,16 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -567,26 +567,26 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -619,31 +619,31 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,12 +660,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -675,35 +675,243 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ESG_J._BERTINO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Bertino</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ESG_Y._ANTONIO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESG_M._POMBO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Pombo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -777,7 +985,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Best net</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -786,22 +994,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>68.2</v>
+        <v>105.9</v>
       </c>
       <c r="E2" t="n">
-        <v>62.2</v>
+        <v>73.3</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-25.8</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -811,20 +1019,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Bailey | P. Carvalhal</t>
+          <t>F. Ferreira | J. Bailey | P. Carvalhal</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>68.2</v>
+        <v>69.2</v>
       </c>
       <c r="E3" t="n">
-        <v>62.2</v>
+        <v>68.8</v>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>90.8</v>
       </c>
       <c r="G3" t="n">
-        <v>-25.8</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="4">
@@ -840,49 +1048,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F. Ferreira | P. Carvalhal</t>
+          <t>J. Bailey | O. Onyeka</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>66.2</v>
       </c>
       <c r="E4" t="n">
-        <v>56.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>87.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-30.6</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>trio</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best net</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | P. Carvalhal</t>
+          <t>J. Bailey | O. Onyeka</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>66.2</v>
       </c>
       <c r="E5" t="n">
-        <v>54.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-34.8</v>
+        <v>-10.3</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1210,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal (15.3 min)</t>
+          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1227,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio (10.7 net)</t>
+          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal</t>
         </is>
       </c>
     </row>
@@ -1112,10 +1320,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -1131,16 +1339,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>-28</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="4">
@@ -1150,16 +1358,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108.1</v>
+        <v>111.5</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="5">
@@ -1169,16 +1377,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-29.8</v>
+        <v>-20.9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>-29.4</v>
+        <v>-20.6</v>
       </c>
     </row>
     <row r="6">
@@ -1188,16 +1396,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.2</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1421,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1245,16 +1453,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.5</v>
+        <v>18.3</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="10">
@@ -1270,7 +1478,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1</v>
@@ -1289,10 +1497,10 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1577,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1525,7 +1733,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with P. Carvalhal and J. Bailey; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with D. Carr, P. Carvalhal, and J. Bailey; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1745,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from J. Bailey and M. Pombo; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from J. Bailey and O. Onyeka; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1769,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially J. Bailey, P. Carvalhal, and Y. Antonio; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially J. Bailey, P. Carvalhal, and D. Carr; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1573,19 +1781,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: J. Bailey | P. Carvalhal and J. Bailey | P. Carvalhal.</t>
+          <t>Most-used lineup to rehearse first: D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+          <t>Recognize the main duo/trio combinations: J. Bailey | P. Carvalhal and F. Ferreira | J. Bailey | P. Carvalhal.</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1805,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose P. Carvalhal and J. Bailey in help-and-recover situations.</t>
+          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Do not lose D. Carr and P. Carvalhal in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1842,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1679,17 +1899,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1715,17 +1935,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.7</v>
+        <v>37.3</v>
       </c>
       <c r="D3" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1735,7 +1955,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
@@ -1751,61 +1971,133 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.8</v>
+        <v>27.2</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ESG_D._CARR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bench spacer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>ESG_J._BERTINO</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>J. Bertino</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="C7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>rotation piece</t>
         </is>
@@ -1822,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1921,12 +2213,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1934,19 +2226,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1967,20 +2259,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1989,10 +2281,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2008,7 +2300,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2022,23 +2314,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2059,32 +2351,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2114,23 +2406,23 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2151,36 +2443,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2192,38 +2484,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ESG_M._POMBO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>M. Pombo</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>42</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>26.2%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>32.1%</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2241,23 +2543,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
     </row>
@@ -2277,23 +2579,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -2313,23 +2615,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -2349,42 +2651,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ESG_J._BAILEY</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>J. Bailey</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2393,23 +2687,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2715,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2441,19 +2735,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2759,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2481,23 +2775,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -2529,19 +2823,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2847,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2569,23 +2863,111 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>62.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2600,24 +2982,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>88</v>
+      </c>
+      <c r="E2" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ESG.xlsx
@@ -515,41 +515,41 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -567,36 +567,36 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -608,12 +608,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -623,79 +623,79 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_D._CARR</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -723,21 +723,21 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -757,111 +757,111 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_J._BERTINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -879,26 +879,26 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,7 +932,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -994,80 +994,80 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>105.9</v>
+        <v>128.5</v>
       </c>
       <c r="E2" t="n">
-        <v>73.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>89.5</v>
+        <v>94.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.2</v>
+        <v>-20.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>trio</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best net</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | P. Carvalhal</t>
+          <t>F. Ferreira | J. Bailey</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>68.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>90.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-22</v>
+        <v>-19.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Best defense</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>J. Bailey | O. Onyeka</t>
+          <t>D. Carr | J. Bailey | P. Carvalhal</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>79.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="F4" t="n">
-        <v>89.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.3</v>
+        <v>-21.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1077,20 +1077,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Bailey | O. Onyeka</t>
+          <t>F. Ferreira | J. Bailey | P. Carvalhal</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.2</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
-        <v>79.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="F5" t="n">
-        <v>89.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.3</v>
+        <v>-22</v>
       </c>
     </row>
   </sheetData>
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.5</v>
+        <v>81</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>-15</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="4">
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>111.5</v>
+        <v>114.4</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="5">
@@ -1377,16 +1377,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-20.9</v>
+        <v>-23.3</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>-20.6</v>
+        <v>-23.2</v>
       </c>
     </row>
     <row r="6">
@@ -1396,16 +1396,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="7">
@@ -1421,10 +1421,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1440,7 +1440,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1</v>
@@ -1453,16 +1453,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="10">
@@ -1478,7 +1478,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
+          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
+          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from J. Bailey and O. Onyeka; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from J. Bailey and P. Carvalhal; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially J. Bailey, P. Carvalhal, and D. Carr; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially J. Bailey, D. Carr, and P. Carvalhal; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: J. Bailey | P. Carvalhal and F. Ferreira | J. Bailey | P. Carvalhal.</t>
+          <t>Recognize the main duo/trio combinations: J. Bailey | P. Carvalhal and F. Ferreira | J. Bailey.</t>
         </is>
       </c>
     </row>
@@ -1899,17 +1899,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1935,17 +1935,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37.3</v>
+        <v>34.8</v>
       </c>
       <c r="D3" t="n">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1955,79 +1955,79 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>spot-up shooter</t>
+          <t>primary handler</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_D._CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27.2</v>
+        <v>35.2</v>
       </c>
       <c r="D4" t="n">
-        <v>8.300000000000001</v>
+        <v>17.3</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESG_D._CARR</t>
+          <t>ESG_F._FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.8</v>
+        <v>25.2</v>
       </c>
       <c r="D5" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>bench spacer</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.5</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2070,36 +2070,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.1</v>
+        <v>15.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2222,23 +2222,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2268,23 +2268,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2314,20 +2314,20 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
         <v>0.9</v>
@@ -2346,41 +2346,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESG_J._BAILEY</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>31</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25.8%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.8%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>61</v>
       </c>
       <c r="H5" t="n">
         <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2397,36 +2397,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2443,32 +2443,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESG_J._BERTINO</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2489,32 +2489,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESG_M._POMBO</t>
+          <t>ESG_Z._JAMES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>Z. James</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2530,38 +2530,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>73</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>32.9%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>36.0%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ESG_O._ONYEKA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2579,23 +2589,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
     </row>
@@ -2615,23 +2625,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>25.1%</t>
         </is>
       </c>
     </row>
@@ -2651,23 +2661,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -2687,15 +2697,15 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -2703,26 +2713,18 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ESG_J._BAILEY</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>J. Bailey</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2731,23 +2733,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2761,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESG_P._CARVALHAL</t>
+          <t>ESG_J._BAILEY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2779,19 +2781,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -2823,19 +2825,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2847,12 +2849,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ESG_Y._ANTONIO</t>
+          <t>ESG_P._CARVALHAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2863,15 +2865,15 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -2879,7 +2881,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2893,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ESG_O._ONYEKA</t>
+          <t>ESG_Y._ANTONIO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2911,19 +2913,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -2935,12 +2937,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ESG_F._FERREIRA</t>
+          <t>ESG_O._ONYEKA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2955,17 +2957,105 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>32.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ESG_Z._JAMES</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Z. James</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ESG_F._FERREIRA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
